--- a/artfynd/A 19977-2026 artfynd.xlsx
+++ b/artfynd/A 19977-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113678570</v>
+        <v>113678568</v>
       </c>
       <c r="B2" t="n">
-        <v>80437</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494107</v>
+        <v>494153</v>
       </c>
       <c r="R2" t="n">
-        <v>6884092</v>
+        <v>6884110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113678576</v>
+        <v>113678572</v>
       </c>
       <c r="B3" t="n">
-        <v>80397</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493988</v>
+        <v>494002</v>
       </c>
       <c r="R3" t="n">
-        <v>6884229</v>
+        <v>6884182</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113678575</v>
+        <v>113678573</v>
       </c>
       <c r="B4" t="n">
-        <v>80437</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494010</v>
+        <v>494004</v>
       </c>
       <c r="R4" t="n">
-        <v>6884214</v>
+        <v>6884197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113678574</v>
+        <v>113678579</v>
       </c>
       <c r="B5" t="n">
-        <v>79332</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494019</v>
+        <v>493973</v>
       </c>
       <c r="R5" t="n">
-        <v>6884211</v>
+        <v>6884191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113678577</v>
+        <v>113678586</v>
       </c>
       <c r="B6" t="n">
-        <v>80437</v>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493981</v>
+        <v>494106</v>
       </c>
       <c r="R6" t="n">
-        <v>6884208</v>
+        <v>6884118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113678572</v>
+        <v>113678587</v>
       </c>
       <c r="B7" t="n">
-        <v>79364</v>
+        <v>79405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494002</v>
+        <v>494136</v>
       </c>
       <c r="R7" t="n">
-        <v>6884182</v>
+        <v>6884133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113678582</v>
+        <v>113678588</v>
       </c>
       <c r="B8" t="n">
-        <v>80437</v>
+        <v>79405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494090</v>
+        <v>494145</v>
       </c>
       <c r="R8" t="n">
-        <v>6884180</v>
+        <v>6884127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,32 +1445,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113678580</v>
+        <v>113678574</v>
       </c>
       <c r="B9" t="n">
-        <v>80437</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493975</v>
+        <v>494019</v>
       </c>
       <c r="R9" t="n">
-        <v>6884179</v>
+        <v>6884211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,32 +1555,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113678584</v>
+        <v>113678569</v>
       </c>
       <c r="B10" t="n">
-        <v>80437</v>
+        <v>80413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494101</v>
+        <v>494047</v>
       </c>
       <c r="R10" t="n">
-        <v>6884158</v>
+        <v>6884116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,32 +1665,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113678569</v>
+        <v>113678570</v>
       </c>
       <c r="B11" t="n">
-        <v>80372</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494047</v>
+        <v>494107</v>
       </c>
       <c r="R11" t="n">
-        <v>6884116</v>
+        <v>6884092</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113678573</v>
+        <v>113678575</v>
       </c>
       <c r="B12" t="n">
-        <v>79364</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494004</v>
+        <v>494010</v>
       </c>
       <c r="R12" t="n">
-        <v>6884197</v>
+        <v>6884214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113678586</v>
+        <v>113678577</v>
       </c>
       <c r="B13" t="n">
-        <v>79364</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494106</v>
+        <v>493981</v>
       </c>
       <c r="R13" t="n">
-        <v>6884118</v>
+        <v>6884208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>113678578</v>
       </c>
       <c r="B14" t="n">
-        <v>80437</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113678585</v>
+        <v>113678580</v>
       </c>
       <c r="B15" t="n">
-        <v>80437</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494103</v>
+        <v>493975</v>
       </c>
       <c r="R15" t="n">
-        <v>6884139</v>
+        <v>6884179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113678579</v>
+        <v>113678581</v>
       </c>
       <c r="B16" t="n">
-        <v>79364</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493973</v>
+        <v>494013</v>
       </c>
       <c r="R16" t="n">
-        <v>6884191</v>
+        <v>6884156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113678581</v>
+        <v>113678582</v>
       </c>
       <c r="B17" t="n">
-        <v>80437</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494013</v>
+        <v>494090</v>
       </c>
       <c r="R17" t="n">
-        <v>6884156</v>
+        <v>6884180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,6 +2428,336 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113678584</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Treflobäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>494101</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6884158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113678585</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Treflobäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494103</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6884139</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113678576</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Treflobäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>493988</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6884229</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 19977-2026 artfynd.xlsx
+++ b/artfynd/A 19977-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678568</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678579</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678586</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678587</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678588</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678570</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678577</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678578</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678580</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678581</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678582</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678584</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678585</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,8 +2857,34 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678576</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>